--- a/Przhevalsky/R_calc_Przhevalsky_Ciliata/Data/Infusoria_abundance_new.xlsx
+++ b/Przhevalsky/R_calc_Przhevalsky_Ciliata/Data/Infusoria_abundance_new.xlsx
@@ -92,7 +92,7 @@
     <t>C. periachtum</t>
   </si>
   <si>
-    <t>Tripalmaria dogieli</t>
+    <t>T. dogieli</t>
   </si>
   <si>
     <t>A. intestinalis</t>
